--- a/ig/DM-MARS-2026/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="269">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260202120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -813,6 +813,12 @@
   </si>
   <si>
     <t>Agent d'autorité d'enregistrement</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Conseiller conjugal et familial</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -1537,7 +1543,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2106,18 +2112,26 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>118</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>118</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>266</v>
+      <c r="B73" t="s" s="2">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
